--- a/new original/_Dialog/Drama/loytel.xlsx
+++ b/new original/_Dialog/Drama/loytel.xlsx
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">Why!</t>
   </si>
   <si>
-    <t xml:space="preserve">考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+    <t xml:space="preserve">考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
   </si>
   <si>
     <t xml:space="preserve">Think about it. This dragon eats gold, doesn’t it? How are we supposed to feed it when we are hardly wealthy?</t>
@@ -3978,7 +3978,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4101,10 +4101,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11540,7 +11536,7 @@
       <c r="I686" s="1" t="n">
         <v>411</v>
       </c>
-      <c r="J686" s="31" t="s">
+      <c r="J686" s="7" t="s">
         <v>784</v>
       </c>
       <c r="K686" s="4" t="s">

--- a/new original/_Dialog/Drama/loytel.xlsx
+++ b/new original/_Dialog/Drama/loytel.xlsx
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">Why!</t>
   </si>
   <si>
-    <t xml:space="preserve">考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+    <t xml:space="preserve">考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
   </si>
   <si>
     <t xml:space="preserve">Think about it. This dragon eats gold, doesn’t it? How are we supposed to feed it when we are hardly wealthy?</t>
@@ -3978,7 +3978,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4101,6 +4101,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11536,7 +11540,7 @@
       <c r="I686" s="1" t="n">
         <v>411</v>
       </c>
-      <c r="J686" s="7" t="s">
+      <c r="J686" s="31" t="s">
         <v>784</v>
       </c>
       <c r="K686" s="4" t="s">
